--- a/Good one/3. Regression/3.3_regression/Control_0_8_GFDD.SI.04_GFDD.SI.02_GFDD.SI.01_3.3_regression_ridge.xlsx
+++ b/Good one/3. Regression/3.3_regression/Control_0_8_GFDD.SI.04_GFDD.SI.02_GFDD.SI.01_3.3_regression_ridge.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Performance" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Regression" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Alpha_selection" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Validation_predictions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +496,21 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>std_err_approx</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>z_approx</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p_value_approx</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>odds_ratio</t>
         </is>
       </c>
@@ -509,6 +525,15 @@
         <v>-0.0532744644170465</v>
       </c>
       <c r="C2" t="n">
+        <v>2.750296059524671</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.01937044713151857</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.984545585756626</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.9481197516328387</v>
       </c>
     </row>
@@ -522,6 +547,15 @@
         <v>-0.003131314827593326</v>
       </c>
       <c r="C3" t="n">
+        <v>0.01143267662452813</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2738916642560566</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7841678776937928</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.9968735826255253</v>
       </c>
     </row>
@@ -535,6 +569,15 @@
         <v>0.1183796553184611</v>
       </c>
       <c r="C4" t="n">
+        <v>0.04826457579109848</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.452723418327321</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01417793045182046</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.125671397384362</v>
       </c>
     </row>
@@ -548,6 +591,15 @@
         <v>0.4091882661965038</v>
       </c>
       <c r="C5" t="n">
+        <v>0.4601127695438965</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8893216908588009</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3738302173595471</v>
+      </c>
+      <c r="F5" t="n">
         <v>1.505595146476658</v>
       </c>
     </row>
@@ -561,6 +613,15 @@
         <v>-0.07239552408682901</v>
       </c>
       <c r="C6" t="n">
+        <v>0.02567486622540916</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.819704042515427</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.004806796021403857</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.9301629212045811</v>
       </c>
     </row>
@@ -574,6 +635,15 @@
         <v>-0.007558083395179173</v>
       </c>
       <c r="C7" t="n">
+        <v>0.01515511034296378</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4987151676324312</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6179800577135346</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.9924704070941079</v>
       </c>
     </row>
@@ -587,6 +657,15 @@
         <v>0.07635980152400791</v>
       </c>
       <c r="C8" t="n">
+        <v>0.1981350838332721</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3853926323732934</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6999465403396143</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.079350856383893</v>
       </c>
     </row>
@@ -600,6 +679,15 @@
         <v>0.04723329637419715</v>
       </c>
       <c r="C9" t="n">
+        <v>0.03259011311579194</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.449313667810183</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1472500058424443</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.048366560669481</v>
       </c>
     </row>
@@ -613,6 +701,15 @@
         <v>0.3966703555606118</v>
       </c>
       <c r="C10" t="n">
+        <v>0.194250735347198</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.042053302148973</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04114624434132833</v>
+      </c>
+      <c r="F10" t="n">
         <v>1.486865712242801</v>
       </c>
     </row>
@@ -626,6 +723,15 @@
         <v>-0.08979169284873337</v>
       </c>
       <c r="C11" t="n">
+        <v>0.08075756506733826</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.111867263133332</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2661952260794022</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.9141215835028539</v>
       </c>
     </row>
@@ -639,6 +745,15 @@
         <v>0.01918591548347888</v>
       </c>
       <c r="C12" t="n">
+        <v>0.01872834339782869</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.024432064060895</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3056312436367524</v>
+      </c>
+      <c r="F12" t="n">
         <v>1.019371147881241</v>
       </c>
     </row>
@@ -652,6 +767,15 @@
         <v>0.005098480854481231</v>
       </c>
       <c r="C13" t="n">
+        <v>0.01929334922478623</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2642610567547908</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7915787661134182</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.005111500224926</v>
       </c>
     </row>
@@ -665,6 +789,15 @@
         <v>0.07984641632190291</v>
       </c>
       <c r="C14" t="n">
+        <v>1.344090705631866</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0594055267158228</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9526291111532165</v>
+      </c>
+      <c r="F14" t="n">
         <v>1.083120705238275</v>
       </c>
     </row>
@@ -678,6 +811,15 @@
         <v>-0.002417437513211471</v>
       </c>
       <c r="C15" t="n">
+        <v>3.092118423871448</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.0007818062511929114</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9993762089261797</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.9975854821356902</v>
       </c>
     </row>
@@ -691,6 +833,15 @@
         <v>-0.003277240521691184</v>
       </c>
       <c r="C16" t="n">
+        <v>2.840421147699745</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.001153786833457844</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.999079411503378</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.9967281237694032</v>
       </c>
     </row>
@@ -704,6 +855,15 @@
         <v>-0.009549875306765883</v>
       </c>
       <c r="C17" t="n">
+        <v>2.07348532454975</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.004605711549388278</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9963251868552802</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.9904955799400285</v>
       </c>
     </row>
@@ -717,6 +877,15 @@
         <v>-0.00947650959548225</v>
       </c>
       <c r="C18" t="n">
+        <v>2.389356472646472</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.003966134691064321</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9968354906603443</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.9905682510185242</v>
       </c>
     </row>
@@ -730,6 +899,15 @@
         <v>-0.001332712697560459</v>
       </c>
       <c r="C19" t="n">
+        <v>3.452518583153025</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.0003860117376525037</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9996920072018871</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.9986681749696278</v>
       </c>
     </row>
@@ -743,6 +921,15 @@
         <v>-0.0427817475353281</v>
       </c>
       <c r="C20" t="n">
+        <v>1.375641838406828</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.03109948123188439</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9751902033876911</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.9581204794051518</v>
       </c>
     </row>
@@ -756,6 +943,15 @@
         <v>-0.04887508131206646</v>
       </c>
       <c r="C21" t="n">
+        <v>1.629400503822854</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.02999574456826121</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9760704469877145</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.9523000823454515</v>
       </c>
     </row>
@@ -769,6 +965,15 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
+        <v>4.328761281083059</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -782,6 +987,15 @@
         <v>-0.07585665974905444</v>
       </c>
       <c r="C23" t="n">
+        <v>1.485704509403456</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.05105770310915501</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9592795400341653</v>
+      </c>
+      <c r="F23" t="n">
         <v>0.9269490661488469</v>
       </c>
     </row>
@@ -795,6 +1009,15 @@
         <v>-0.006658336879674669</v>
       </c>
       <c r="C24" t="n">
+        <v>2.296279917326792</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.002899619000903842</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9976864420089537</v>
+      </c>
+      <c r="F24" t="n">
         <v>0.9933637807292711</v>
       </c>
     </row>
@@ -808,6 +1031,15 @@
         <v>-0.02191063794954556</v>
       </c>
       <c r="C25" t="n">
+        <v>2.146159047299868</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.01020923308415182</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9918543520461266</v>
+      </c>
+      <c r="F25" t="n">
         <v>0.9783276565104735</v>
       </c>
     </row>
@@ -821,6 +1053,15 @@
         <v>-0.008848000341924334</v>
       </c>
       <c r="C26" t="n">
+        <v>2.129487069697374</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.004154991344080686</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9966848060951832</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.9911910280206233</v>
       </c>
     </row>
@@ -834,6 +1075,15 @@
         <v>-0.003214084525508022</v>
       </c>
       <c r="C27" t="n">
+        <v>2.998449077405037</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.001071915661242313</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9991447352071956</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.9967910751148402</v>
       </c>
     </row>
@@ -847,6 +1097,15 @@
         <v>-0.06895855626022801</v>
       </c>
       <c r="C28" t="n">
+        <v>1.819916731207596</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.03789105022100156</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9697745488153957</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.9333653614277977</v>
       </c>
     </row>
@@ -860,6 +1119,15 @@
         <v>-0.0244794176564638</v>
       </c>
       <c r="C29" t="n">
+        <v>1.704765039442244</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.01435940853437073</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9885432433459503</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.9758177733283538</v>
       </c>
     </row>
@@ -873,6 +1141,15 @@
         <v>-0.01100600089619447</v>
       </c>
       <c r="C30" t="n">
+        <v>1.977698818971791</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.00556505408741484</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9955597521825817</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.989054343545114</v>
       </c>
     </row>
@@ -886,6 +1163,15 @@
         <v>-0.01895023461694396</v>
       </c>
       <c r="C31" t="n">
+        <v>1.772581854438767</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.01069075290909145</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9914701757928464</v>
+      </c>
+      <c r="F31" t="n">
         <v>0.981228192224626</v>
       </c>
     </row>
@@ -899,6 +1185,15 @@
         <v>-0.005603009168822749</v>
       </c>
       <c r="C32" t="n">
+        <v>2.696889745921247</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.002077581843045936</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9983423307161419</v>
+      </c>
+      <c r="F32" t="n">
         <v>0.994412658411527</v>
       </c>
     </row>
@@ -912,6 +1207,15 @@
         <v>0.4384074792817629</v>
       </c>
       <c r="C33" t="n">
+        <v>1.561785882523167</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.2807090806669907</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7789335433245422</v>
+      </c>
+      <c r="F33" t="n">
         <v>1.550236467979383</v>
       </c>
     </row>
@@ -925,6 +1229,15 @@
         <v>0.1482384299073783</v>
       </c>
       <c r="C34" t="n">
+        <v>1.122371375452118</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1320760963345705</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8949241026217833</v>
+      </c>
+      <c r="F34" t="n">
         <v>1.159789391876548</v>
       </c>
     </row>
@@ -938,6 +1251,15 @@
         <v>-0.07739278369296529</v>
       </c>
       <c r="C35" t="n">
+        <v>1.482992834614943</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.05218688983959942</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9583797790916229</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.9255262505838604</v>
       </c>
     </row>
@@ -951,6 +1273,15 @@
         <v>-0.001278291274594212</v>
       </c>
       <c r="C36" t="n">
+        <v>3.471907906992075</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.0003681812158726506</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9997062338989147</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.9987225253916809</v>
       </c>
     </row>
@@ -964,6 +1295,15 @@
         <v>-0.0009959113749416022</v>
       </c>
       <c r="C37" t="n">
+        <v>3.616073562771406</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.0002754123658309437</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9997802527282273</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.999004584380202</v>
       </c>
     </row>
@@ -977,6 +1317,15 @@
         <v>-0.0002986929012107817</v>
       </c>
       <c r="C38" t="n">
+        <v>4.065816010344271</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-7.346444119725181e-05</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9999413838566534</v>
+      </c>
+      <c r="F38" t="n">
         <v>0.9997013517030727</v>
       </c>
     </row>
@@ -990,6 +1339,15 @@
         <v>-0.02484147576423663</v>
       </c>
       <c r="C39" t="n">
+        <v>1.679786710673856</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.0147884702304088</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9882009380003834</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.9754645345421535</v>
       </c>
     </row>
@@ -1003,6 +1361,15 @@
         <v>-0.01031237278013644</v>
       </c>
       <c r="C40" t="n">
+        <v>2.659736406019362</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.003877216086826526</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9969064368962481</v>
+      </c>
+      <c r="F40" t="n">
         <v>0.9897406174280216</v>
       </c>
     </row>
@@ -1016,6 +1383,15 @@
         <v>-0.01412413192373312</v>
       </c>
       <c r="C41" t="n">
+        <v>1.981078472355002</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.007129516634918098</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9943115169419918</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.9859751456746473</v>
       </c>
     </row>
@@ -1029,6 +1405,15 @@
         <v>-0.002948582711215375</v>
       </c>
       <c r="C42" t="n">
+        <v>3.060228958664139</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.0009635170279881608</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9992312247582482</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.9970557600893696</v>
       </c>
     </row>
@@ -1042,6 +1427,15 @@
         <v>-0.001101979595962073</v>
       </c>
       <c r="C43" t="n">
+        <v>3.567480706246421</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.0003088957409167148</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9997535368613443</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.9988986273605812</v>
       </c>
     </row>
@@ -1055,6 +1449,15 @@
         <v>-0.0279215273409692</v>
       </c>
       <c r="C44" t="n">
+        <v>1.686105911979238</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.0165597707371736</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9867878184550983</v>
+      </c>
+      <c r="F44" t="n">
         <v>0.9724646756960422</v>
       </c>
     </row>
@@ -1068,6 +1471,15 @@
         <v>-0.01731864027012511</v>
       </c>
       <c r="C45" t="n">
+        <v>2.022324105538686</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.008563731314230638</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9931672145181741</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.9828304653704514</v>
       </c>
     </row>
@@ -1081,6 +1493,15 @@
         <v>-0.00933156960574052</v>
       </c>
       <c r="C46" t="n">
+        <v>2.438909034360625</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.00382612449840174</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9969472017834526</v>
+      </c>
+      <c r="F46" t="n">
         <v>0.990711834375899</v>
       </c>
     </row>
@@ -1094,6 +1515,15 @@
         <v>-0.01960879440118575</v>
       </c>
       <c r="C47" t="n">
+        <v>1.731780034986211</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.01132291284403327</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9909658157018268</v>
+      </c>
+      <c r="F47" t="n">
         <v>0.9805822075311798</v>
       </c>
     </row>
@@ -1107,6 +1537,15 @@
         <v>-0.07299060046539883</v>
       </c>
       <c r="C48" t="n">
+        <v>1.44384555304805</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.05055291427210551</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9596817837826734</v>
+      </c>
+      <c r="F48" t="n">
         <v>0.9296095678820256</v>
       </c>
     </row>
@@ -1120,6 +1559,15 @@
         <v>0.3589202751090894</v>
       </c>
       <c r="C49" t="n">
+        <v>1.469437111460479</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.2442569826975155</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8070317973866096</v>
+      </c>
+      <c r="F49" t="n">
         <v>1.431782648305847</v>
       </c>
     </row>
@@ -1133,6 +1581,15 @@
         <v>-0.0006762092465824093</v>
       </c>
       <c r="C50" t="n">
+        <v>3.812335425079774</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.0001773740164975802</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.999858476011491</v>
+      </c>
+      <c r="F50" t="n">
         <v>0.9993240193313651</v>
       </c>
     </row>
@@ -1146,6 +1603,15 @@
         <v>-0.006974742050766976</v>
       </c>
       <c r="C51" t="n">
+        <v>2.303165478210386</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.00302832867058537</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9975837470018557</v>
+      </c>
+      <c r="F51" t="n">
         <v>0.9930495250109614</v>
       </c>
     </row>
@@ -1159,6 +1625,15 @@
         <v>-0.04039242994521563</v>
       </c>
       <c r="C52" t="n">
+        <v>1.646805695205901</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.02452774487166523</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9804316531616563</v>
+      </c>
+      <c r="F52" t="n">
         <v>0.9604124705770694</v>
       </c>
     </row>
@@ -1172,6 +1647,15 @@
         <v>0.0961691488437522</v>
       </c>
       <c r="C53" t="n">
+        <v>2.041462617514673</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.04710796466154786</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9624271795048716</v>
+      </c>
+      <c r="F53" t="n">
         <v>1.100945271864882</v>
       </c>
     </row>
@@ -1185,6 +1669,15 @@
         <v>-0.009812764313269377</v>
       </c>
       <c r="C54" t="n">
+        <v>2.214470545369794</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.004431201098513932</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9964644246281773</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.9902352237649594</v>
       </c>
     </row>
@@ -1198,6 +1691,15 @@
         <v>-0.06786993897743525</v>
       </c>
       <c r="C55" t="n">
+        <v>1.926057070174924</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.03523776113823632</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9718901518830704</v>
+      </c>
+      <c r="F55" t="n">
         <v>0.9343819923520056</v>
       </c>
     </row>
@@ -1211,6 +1713,15 @@
         <v>-0.001205037709037774</v>
       </c>
       <c r="C56" t="n">
+        <v>3.50797122957567</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.0003435141368544054</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9997259153791768</v>
+      </c>
+      <c r="F56" t="n">
         <v>0.9987956880573478</v>
       </c>
     </row>
@@ -1224,6 +1735,15 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
+        <v>4.328761281083059</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1237,6 +1757,15 @@
         <v>-0.01534162815848867</v>
       </c>
       <c r="C58" t="n">
+        <v>1.89705332211326</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.008087083256784035</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9935475114606711</v>
+      </c>
+      <c r="F58" t="n">
         <v>0.9847754551047933</v>
       </c>
     </row>
@@ -1250,6 +1779,15 @@
         <v>-0.03028943369331627</v>
       </c>
       <c r="C59" t="n">
+        <v>2.088003702032833</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.01450640804124397</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.98842596692457</v>
+      </c>
+      <c r="F59" t="n">
         <v>0.9701646945576646</v>
       </c>
     </row>
@@ -1263,6 +1801,15 @@
         <v>-0.004895463656557705</v>
       </c>
       <c r="C60" t="n">
+        <v>2.548095778135619</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.001921224350577434</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.99846708569586</v>
+      </c>
+      <c r="F60" t="n">
         <v>0.9951164995957982</v>
       </c>
     </row>
@@ -1276,6 +1823,15 @@
         <v>-0.01029400205996181</v>
       </c>
       <c r="C61" t="n">
+        <v>3.736697311477442</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.002754839689140272</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9978019587247562</v>
+      </c>
+      <c r="F61" t="n">
         <v>0.9897587998429612</v>
       </c>
     </row>
@@ -1289,6 +1845,15 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
+        <v>4.328761281083058</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1302,6 +1867,15 @@
         <v>-0.01165553152771773</v>
       </c>
       <c r="C63" t="n">
+        <v>2.129414831164486</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-0.005473584271667639</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9956327334247025</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.9884121310436648</v>
       </c>
     </row>
@@ -1315,6 +1889,15 @@
         <v>-0.0007256933581521974</v>
       </c>
       <c r="C64" t="n">
+        <v>3.786133638145714</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.0001916713532878916</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9998470683873998</v>
+      </c>
+      <c r="F64" t="n">
         <v>0.999274569893589</v>
       </c>
     </row>
@@ -1328,6 +1911,15 @@
         <v>-0.0009626740629738163</v>
       </c>
       <c r="C65" t="n">
+        <v>3.6445701542373</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.0002641392598396217</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9997892473651228</v>
+      </c>
+      <c r="F65" t="n">
         <v>0.9990377891590461</v>
       </c>
     </row>
@@ -1341,6 +1933,15 @@
         <v>-0.0219153525564235</v>
       </c>
       <c r="C66" t="n">
+        <v>1.869699633889772</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.01172132259063999</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9906479518186153</v>
+      </c>
+      <c r="F66" t="n">
         <v>0.9783230440910481</v>
       </c>
     </row>
@@ -1354,6 +1955,15 @@
         <v>-0.005494650294741446</v>
       </c>
       <c r="C67" t="n">
+        <v>2.529714234548962</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.002172043869500983</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.99826696109382</v>
+      </c>
+      <c r="F67" t="n">
         <v>0.994520417685796</v>
       </c>
     </row>
@@ -1367,6 +1977,15 @@
         <v>-0.03267280919136663</v>
       </c>
       <c r="C68" t="n">
+        <v>1.8304270838678</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.01784982831565575</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9857586538323109</v>
+      </c>
+      <c r="F68" t="n">
         <v>0.9678551811077286</v>
       </c>
     </row>
@@ -1380,6 +1999,15 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
+        <v>4.328761281083058</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1393,6 +2021,15 @@
         <v>-0.0006222042030585224</v>
       </c>
       <c r="C70" t="n">
+        <v>3.842036121263628</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.0001619464740622694</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.999870785409234</v>
+      </c>
+      <c r="F70" t="n">
         <v>0.9993779893258364</v>
       </c>
     </row>
@@ -1406,6 +2043,15 @@
         <v>-0.005052301166045022</v>
       </c>
       <c r="C71" t="n">
+        <v>2.604700290444328</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.001939686183696461</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.998452355311698</v>
+      </c>
+      <c r="F71" t="n">
         <v>0.994960440240652</v>
       </c>
     </row>
@@ -1419,6 +2065,15 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
+        <v>4.328761281083059</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1432,6 +2087,15 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
+        <v>4.32876128108306</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1445,6 +2109,15 @@
         <v>-0.1034530845134381</v>
       </c>
       <c r="C74" t="n">
+        <v>3.209609323041419</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-0.03223229810891941</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9742867993876301</v>
+      </c>
+      <c r="F74" t="n">
         <v>0.9017183263035219</v>
       </c>
     </row>
@@ -1458,6 +2131,15 @@
         <v>-0.01352181028228106</v>
       </c>
       <c r="C75" t="n">
+        <v>1.97757239556494</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-0.006837580415567156</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9945444426633668</v>
+      </c>
+      <c r="F75" t="n">
         <v>0.9865691987303671</v>
       </c>
     </row>
@@ -1471,6 +2153,15 @@
         <v>-0.00116310433283906</v>
       </c>
       <c r="C76" t="n">
+        <v>3.530947021484249</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-0.000329402940843373</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.999737174483971</v>
+      </c>
+      <c r="F76" t="n">
         <v>0.9988375718108382</v>
       </c>
     </row>
@@ -1484,6 +2175,15 @@
         <v>-0.0001240033948741147</v>
       </c>
       <c r="C77" t="n">
+        <v>4.212831294376335</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-2.943469277766845e-05</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9999765145130841</v>
+      </c>
+      <c r="F77" t="n">
         <v>0.9998760042932291</v>
       </c>
     </row>
@@ -1497,6 +2197,15 @@
         <v>-0.009753936775539939</v>
       </c>
       <c r="C78" t="n">
+        <v>2.136976743179817</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.004564362624286729</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.9963581781774392</v>
+      </c>
+      <c r="F78" t="n">
         <v>0.9902934785784233</v>
       </c>
     </row>
@@ -1510,6 +2219,15 @@
         <v>-0.06417301351942138</v>
       </c>
       <c r="C79" t="n">
+        <v>1.707146941614361</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.03759079664152182</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9700139459532381</v>
+      </c>
+      <c r="F79" t="n">
         <v>0.937842726022686</v>
       </c>
     </row>
@@ -1523,6 +2241,15 @@
         <v>-0.1181429952086893</v>
       </c>
       <c r="C80" t="n">
+        <v>2.285798905760456</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.05168564693550094</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9587791740392667</v>
+      </c>
+      <c r="F80" t="n">
         <v>0.8885689824225432</v>
       </c>
     </row>
@@ -1536,6 +2263,15 @@
         <v>-0.009595270575909459</v>
       </c>
       <c r="C81" t="n">
+        <v>2.062385837297894</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-0.004652509924370424</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9962878475544825</v>
+      </c>
+      <c r="F81" t="n">
         <v>0.9904506171471483</v>
       </c>
     </row>
@@ -1549,6 +2285,15 @@
         <v>-0.01873731833240365</v>
       </c>
       <c r="C82" t="n">
+        <v>1.798074471380772</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.01042076878941223</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9916855799520059</v>
+      </c>
+      <c r="F82" t="n">
         <v>0.981437133928357</v>
       </c>
     </row>
@@ -1562,6 +2307,15 @@
         <v>-0.03477584958344685</v>
       </c>
       <c r="C83" t="n">
+        <v>1.4600206719915</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-0.02381873781006939</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9809971936780655</v>
+      </c>
+      <c r="F83" t="n">
         <v>0.9658218813733132</v>
       </c>
     </row>
@@ -1575,6 +2329,15 @@
         <v>-0.001359506223524015</v>
       </c>
       <c r="C84" t="n">
+        <v>3.448214166100024</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.0003942638589242948</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9996854229622316</v>
+      </c>
+      <c r="F84" t="n">
         <v>0.998641417486418</v>
       </c>
     </row>
@@ -1588,6 +2351,15 @@
         <v>-0.004038748591936308</v>
       </c>
       <c r="C85" t="n">
+        <v>2.68109041896451</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-0.001506382837135404</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.998798080846155</v>
+      </c>
+      <c r="F85" t="n">
         <v>0.9959693961845671</v>
       </c>
     </row>
@@ -1601,6 +2373,15 @@
         <v>-0.06616405168901343</v>
       </c>
       <c r="C86" t="n">
+        <v>1.660328072068315</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-0.03984998675990047</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9682127241845994</v>
+      </c>
+      <c r="F86" t="n">
         <v>0.9359773030385301</v>
       </c>
     </row>
@@ -1614,6 +2395,15 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
+        <v>4.328761281083058</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1627,6 +2417,15 @@
         <v>-0.00257222945788765</v>
       </c>
       <c r="C88" t="n">
+        <v>3.010319257988793</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-0.0008544706515966575</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.999318231142394</v>
+      </c>
+      <c r="F88" t="n">
         <v>0.9974310758896595</v>
       </c>
     </row>
@@ -1640,6 +2439,15 @@
         <v>-0.02035090297371528</v>
       </c>
       <c r="C89" t="n">
+        <v>1.647136093001706</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-0.01235532574398769</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.990142127153229</v>
+      </c>
+      <c r="F89" t="n">
         <v>0.9798547790177532</v>
       </c>
     </row>
@@ -1653,6 +2461,15 @@
         <v>-0.03561423336471942</v>
       </c>
       <c r="C90" t="n">
+        <v>2.592686875468498</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-0.01373641904145634</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9890402679910463</v>
+      </c>
+      <c r="F90" t="n">
         <v>0.9650124913095319</v>
       </c>
     </row>
@@ -1666,6 +2483,15 @@
         <v>-0.01545332483559731</v>
       </c>
       <c r="C91" t="n">
+        <v>2.401604519147051</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-0.006434583509646995</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9948659805905214</v>
+      </c>
+      <c r="F91" t="n">
         <v>0.9846654651016331</v>
       </c>
     </row>
@@ -1679,6 +2505,15 @@
         <v>-0.002354684862407659</v>
       </c>
       <c r="C92" t="n">
+        <v>3.094409310150124</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.0007609480926404732</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9993928513239039</v>
+      </c>
+      <c r="F92" t="n">
         <v>0.9976480852333323</v>
       </c>
     </row>
@@ -1692,6 +2527,15 @@
         <v>0.1125001269569896</v>
       </c>
       <c r="C93" t="n">
+        <v>1.376254925098482</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.08174366892742584</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9348505517520231</v>
+      </c>
+      <c r="F93" t="n">
         <v>1.119072398986835</v>
       </c>
     </row>
@@ -1705,6 +2549,15 @@
         <v>-0.001317697994136627</v>
       </c>
       <c r="C94" t="n">
+        <v>3.458654415183414</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.0003809857349008225</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9996960173715903</v>
+      </c>
+      <c r="F94" t="n">
         <v>0.9986831697886649</v>
       </c>
     </row>
@@ -1718,6 +2571,15 @@
         <v>-0.00286947808378992</v>
       </c>
       <c r="C95" t="n">
+        <v>2.994124020373757</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-0.0009583698150992832</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9992353316380473</v>
+      </c>
+      <c r="F95" t="n">
         <v>0.9971346349334352</v>
       </c>
     </row>
@@ -1731,6 +2593,15 @@
         <v>-0.00972943830277254</v>
       </c>
       <c r="C96" t="n">
+        <v>2.148658160190648</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.004528146209124888</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9963870743973217</v>
+      </c>
+      <c r="F96" t="n">
         <v>0.9903177395534173</v>
       </c>
     </row>
@@ -1744,6 +2615,15 @@
         <v>-0.002784380332622214</v>
       </c>
       <c r="C97" t="n">
+        <v>3.018184742429253</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-0.0009225347585519712</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9992639238637562</v>
+      </c>
+      <c r="F97" t="n">
         <v>0.9972194924590206</v>
       </c>
     </row>
@@ -1757,6 +2637,15 @@
         <v>-0.02727695622077358</v>
       </c>
       <c r="C98" t="n">
+        <v>1.924827599502667</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-0.01417111653418796</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9886934633401065</v>
+      </c>
+      <c r="F98" t="n">
         <v>0.9730917004007051</v>
       </c>
     </row>
@@ -1770,6 +2659,15 @@
         <v>-0.03726459568001465</v>
       </c>
       <c r="C99" t="n">
+        <v>1.582331809400914</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-0.02355043073685245</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9812112117125503</v>
+      </c>
+      <c r="F99" t="n">
         <v>0.963421184537636</v>
       </c>
     </row>
@@ -1783,6 +2681,15 @@
         <v>-0.0857242550945326</v>
       </c>
       <c r="C100" t="n">
+        <v>1.952863985130767</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.04389668494439071</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9649867577867002</v>
+      </c>
+      <c r="F100" t="n">
         <v>0.9178472880426576</v>
       </c>
     </row>
@@ -1796,6 +2703,15 @@
         <v>-0.0006656436280844489</v>
       </c>
       <c r="C101" t="n">
+        <v>3.808749022276193</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.0001747669967727738</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.999860556112247</v>
+      </c>
+      <c r="F101" t="n">
         <v>0.9993345778634878</v>
       </c>
     </row>
@@ -1809,6 +2725,15 @@
         <v>-0.006901803021991139</v>
       </c>
       <c r="C102" t="n">
+        <v>2.408594617423844</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.002865489681021162</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9977136731532239</v>
+      </c>
+      <c r="F102" t="n">
         <v>0.9931219597204686</v>
       </c>
     </row>
@@ -1822,6 +2747,15 @@
         <v>-0.02909467441621966</v>
       </c>
       <c r="C103" t="n">
+        <v>1.841573179754555</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-0.01579881523909759</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.987394893621738</v>
+      </c>
+      <c r="F103" t="n">
         <v>0.9713245005333099</v>
       </c>
     </row>
@@ -1835,6 +2769,15 @@
         <v>-0.01837801001407149</v>
       </c>
       <c r="C104" t="n">
+        <v>1.75632899899257</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-0.01046387665671586</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9916511867254439</v>
+      </c>
+      <c r="F104" t="n">
         <v>0.9817898358150638</v>
       </c>
     </row>
@@ -1848,6 +2791,15 @@
         <v>0.06032662603382391</v>
       </c>
       <c r="C105" t="n">
+        <v>2.802532455235852</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.0215257546513398</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9828262589796795</v>
+      </c>
+      <c r="F105" t="n">
         <v>1.06218342665208</v>
       </c>
     </row>
@@ -1861,6 +2813,15 @@
         <v>0.3542849477522518</v>
       </c>
       <c r="C106" t="n">
+        <v>1.146074525184933</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.3091290661879807</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.7572233496649636</v>
+      </c>
+      <c r="F106" t="n">
         <v>1.425161225114936</v>
       </c>
     </row>
@@ -1874,6 +2835,15 @@
         <v>-0.0480547444994794</v>
       </c>
       <c r="C107" t="n">
+        <v>1.65619470969854</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.02901515396594057</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.976852504565821</v>
+      </c>
+      <c r="F107" t="n">
         <v>0.9530816096736202</v>
       </c>
     </row>
@@ -1887,6 +2857,15 @@
         <v>0.3340761068286449</v>
       </c>
       <c r="C108" t="n">
+        <v>1.651732991205093</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.2022579367291715</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.8397150819678703</v>
+      </c>
+      <c r="F108" t="n">
         <v>1.396649434088894</v>
       </c>
     </row>
@@ -1900,6 +2879,15 @@
         <v>-0.06178914660681054</v>
       </c>
       <c r="C109" t="n">
+        <v>1.63683193709146</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.03774923081999835</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9698876234279862</v>
+      </c>
+      <c r="F109" t="n">
         <v>0.9400810851816368</v>
       </c>
     </row>
@@ -1913,6 +2901,15 @@
         <v>0.1914970636423679</v>
       </c>
       <c r="C110" t="n">
+        <v>1.623164884524799</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.1179775791529835</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9060854230420832</v>
+      </c>
+      <c r="F110" t="n">
         <v>1.211061277025748</v>
       </c>
     </row>
@@ -1926,6 +2923,15 @@
         <v>-0.2169356623495369</v>
       </c>
       <c r="C111" t="n">
+        <v>1.634080555381346</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.1327570183949166</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.894385547740336</v>
+      </c>
+      <c r="F111" t="n">
         <v>0.8049817582739863</v>
       </c>
     </row>
@@ -1939,6 +2945,15 @@
         <v>0.03413362782836373</v>
       </c>
       <c r="C112" t="n">
+        <v>1.634208089654169</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.02088695316371068</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9833358342221314</v>
+      </c>
+      <c r="F112" t="n">
         <v>1.034722865259762</v>
       </c>
     </row>
@@ -1952,6 +2967,15 @@
         <v>-0.2277341956265354</v>
       </c>
       <c r="C113" t="n">
+        <v>1.656694831405604</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-0.13746297224415</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.8906648587280273</v>
+      </c>
+      <c r="F113" t="n">
         <v>0.7963359012719029</v>
       </c>
     </row>
@@ -1965,6 +2989,15 @@
         <v>-0.1065222581335403</v>
       </c>
       <c r="C114" t="n">
+        <v>1.651471310147108</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.06450142819862344</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9485709699435829</v>
+      </c>
+      <c r="F114" t="n">
         <v>0.8989550388772456</v>
       </c>
     </row>
@@ -2216,4 +3249,4833 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E253"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>actual_crisis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_crisis_prob</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.006481244113540892</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01039020905322446</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06516910131138158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.03819907099887802</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3713170710590059</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4551423973175975</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4687715930853287</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05906179048618877</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1261950670294415</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.05085698772458661</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04843502297734307</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03442461352095149</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.02928858797379175</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3589440455747257</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1411824263564329</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3308535401312476</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.06944689275603513</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.007261317626117415</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.006385697777815566</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1167671610525504</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.005721162423846834</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.001532863990642472</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.00186032727177308</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.08594439902189142</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.07187949489375441</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.06211036021109684</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1076805463519044</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.06068333523287585</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.09593584318405579</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3421141557182693</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1705614560577771</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1544993677403313</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.03274820560940949</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.03517088629653528</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0316424587663568</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1109536838574866</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.07349295083365673</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.02905022995370292</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.05043179183198304</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1049906803684229</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.1144719572006198</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.06894585730531197</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.06265436825594121</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.04028841906171594</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.07140049638605832</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.03076256777575293</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.02343396604573589</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.03374350103915651</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.2086077067495184</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.1078123776462616</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.1497109428730136</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3322557578156688</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.2054109910222346</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.2138902260817482</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2334578491869145</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1374150544697118</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.1221632442573915</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Egypt, Arab Rep.</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.5800604725979561</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Egypt, Arab Rep.</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3188570178019139</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Egypt, Arab Rep.</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1494564714117153</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01622025095983117</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01451198851041523</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01686753180151598</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01012333678035397</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.003325293214507499</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.005716009068095073</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.00547905523068283</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.2110734155507888</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.06877724915214407</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.08240655619746633</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.04535305674188565</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01736219778254591</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01925678192393969</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.06874256206526574</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.02594780902544416</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.04701910812864381</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4657505835818847</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.6069675757446774</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.7319499684453192</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.02411507243518635</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01375595091324455</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.02694405534885673</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.0382866988995926</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.05538095283452981</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.0544595059706264</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.3334176865685244</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.2275411687151397</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.3717617842718547</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR, China</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.06645072284759446</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR, China</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.09753205409226431</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR, China</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.3253867232911867</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.3824436154876784</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.427201356623352</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.0448219995972257</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.3387925991559453</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.4140343393870607</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.3499449677647959</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.07098422904929599</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.05955361398793628</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.07645457626669422</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.07376568996747894</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.05748044008518136</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.4907142533757231</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.2772994324296758</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.3672106131832964</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.3567523851744555</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.263176090020003</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.2493028853226263</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.05180836006357656</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.0310771384169415</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.2643233299503023</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.5264208283110636</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.4355037441509387</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.4475963883936729</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.04994300879295933</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.0377694372314732</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.2144989074779946</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.2015573713184046</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.01327317321484602</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.01591559002533121</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.1423793664892936</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.1158540771790726</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.1530377346265599</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.01643872175586314</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.02831527567072106</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.06391669965454079</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.06514317305305253</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.8422014805353768</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.1625636145385401</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.1660746537015268</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.07468260582050383</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4045289594879123</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.09322550010380463</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.1033679059480883</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.1475794164774393</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.09292026532654837</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.1612061319134439</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.07212017905594818</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.07937218301463338</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.03821729511602308</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.05076218250316204</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.03218046534488673</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.05266331787944836</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.008169731898133956</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.01321381815237626</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.02000904354429614</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.06404709773232536</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.08755584765370195</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.0385844221711342</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.1397636084823355</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>North Macedonia</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.0510552885234323</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>North Macedonia</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.03671104546732218</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>North Macedonia</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.03969883645396419</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.009398411033306331</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.005958014614782719</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.01697638133479908</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.006369691989268914</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.005633138723622235</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.004530334932547072</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.0164625591560103</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.02912576018938368</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.03081049079860447</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.1779705282218155</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.2445527444296171</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.1032570741574309</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.5214502373267377</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.3036954831764443</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.2386898892779674</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.02287731052360633</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.02209231032247424</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.03178556501776604</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.1406818734624077</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.08337948060721725</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.1030940296647737</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.1574265953707533</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.1278523105887311</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.1687900152802073</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.07456315777116303</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.07520969352304593</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.1248279382480918</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.01075761732651723</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.01284113579548882</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.04077954548843124</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.04837090637546722</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.09468101926304848</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.8990035711989007</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.9448027670127395</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.9999999959774744</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.2423823552285953</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.2222798698113002</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.4734294086193508</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.01370435745011</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.01501238913037244</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.01720232940986222</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.09412047207356991</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.1000535101514848</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.3171102079702751</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.9979299719026005</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.4493359859500433</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.997784053308775</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.4386557965844485</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.4245720199301278</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.1137507423062262</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.03044406880930692</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.02078380004160811</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.02780889862271453</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Slovak Republic</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.03704273633073403</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Slovak Republic</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.02987991725223022</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Slovak Republic</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.01727172541556509</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.03529274166955499</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.04437395901740727</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.07570629090976488</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.03446252617318055</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.0341318744764986</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.04373788482525873</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.1905331398152977</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.2175069657562899</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.1361685797790927</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.02731072005853691</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.02477392064044295</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.0361932713379087</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.2050003802638524</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.1121657923955669</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.169605989358221</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.1235474635390728</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.09775966481635873</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.09018455155997095</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.6877522043061275</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.5299821497178401</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.07677302226758666</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.05590987418500844</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.05723160855094031</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.09097287700191529</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.2002086697225633</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.2869002873902187</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.04049109490732425</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.02751020165523167</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.06659157759766537</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.09951284601518554</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.08806284071637972</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.04547422805249249</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.7860029746119075</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.7344990520053806</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.8171973346305844</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.08263138611120917</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.02803777129861387</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.1146194339150473</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.229596887127133</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.1324907021951027</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.2224911930529955</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.2486205937872246</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.3560864694200708</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>